--- a/pre primary oral marks slip/nursery/nur, orals.xlsx
+++ b/pre primary oral marks slip/nursery/nur, orals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\2nd term exam 2082\pre primary oral marks slip\nursery\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Third Term 2082\pre primary oral marks slip\nursery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ADE61A-D3DC-41F8-835D-7C1312E27DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2A4D23-AE6E-4145-8DF7-C697CDDA3E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nur (Danfe)" sheetId="1" r:id="rId1"/>
@@ -209,10 +209,10 @@
     <t>DARSHAN BHUSAL</t>
   </si>
   <si>
-    <t>Nur. Dove Rhymes &amp; Conv.</t>
-  </si>
-  <si>
-    <t>Nur (Danfe), Rhymes &amp; Conv.</t>
+    <t>Nur (Danfe), ________________</t>
+  </si>
+  <si>
+    <t>Nur. Dove, _______________</t>
   </si>
 </sst>
 </file>
@@ -293,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -312,9 +312,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -645,10 +642,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" ht="15.75">
-      <c r="A1" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="14"/>
       <c r="C1" s="5">
         <v>1</v>
       </c>
@@ -1231,18 +1228,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C9282C8-B0CC-4101-A159-2157F99CBC8D}">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75">
-      <c r="A1" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="15"/>
+    <row r="1" spans="1:11" ht="15.75">
+      <c r="A1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="14"/>
       <c r="C1" s="5">
         <v>1</v>
       </c>
@@ -1270,11 +1267,8 @@
       <c r="K1" s="5">
         <v>9</v>
       </c>
-      <c r="L1" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -1290,13 +1284,12 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="9"/>
@@ -1308,13 +1301,12 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>58</v>
       </c>
       <c r="C4" s="9"/>
@@ -1326,13 +1318,12 @@
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="9"/>
@@ -1344,13 +1335,12 @@
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-    </row>
-    <row r="6" spans="1:12">
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="9"/>
@@ -1362,13 +1352,12 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12">
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C7" s="9"/>
@@ -1380,13 +1369,12 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="9"/>
@@ -1398,13 +1386,12 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12">
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>53</v>
       </c>
       <c r="C9" s="9"/>
@@ -1416,13 +1403,12 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="1:12">
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C10" s="9"/>
@@ -1434,13 +1420,12 @@
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="9"/>
@@ -1452,13 +1437,12 @@
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="9"/>
@@ -1470,13 +1454,12 @@
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="9"/>
@@ -1488,13 +1471,12 @@
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C14" s="9"/>
@@ -1506,13 +1488,12 @@
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>47</v>
       </c>
       <c r="C15" s="9"/>
@@ -1524,13 +1505,12 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="9"/>
@@ -1542,13 +1522,12 @@
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12">
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="9"/>
@@ -1560,13 +1539,12 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="1:12">
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="9"/>
@@ -1578,13 +1556,12 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12">
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="9"/>
@@ -1596,13 +1573,12 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="1:12">
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
         <v>19</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="9"/>
@@ -1614,13 +1590,12 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="1:12">
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
         <v>20</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="9"/>
@@ -1632,13 +1607,12 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="1:12">
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
         <v>21</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="12" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="9"/>
@@ -1650,13 +1624,12 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="1:12">
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="9"/>
@@ -1668,13 +1641,12 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="1:12">
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="9"/>
@@ -1686,13 +1658,12 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="1:12">
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C25" s="9"/>
@@ -1704,13 +1675,12 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-    </row>
-    <row r="26" spans="1:12">
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
         <v>25</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="12" t="s">
         <v>60</v>
       </c>
       <c r="C26" s="9"/>
@@ -1722,13 +1692,12 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-    </row>
-    <row r="27" spans="1:12">
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C27" s="9"/>
@@ -1740,13 +1709,12 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-    </row>
-    <row r="28" spans="1:12">
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C28" s="9"/>
@@ -1758,13 +1726,12 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="1:12">
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
         <v>28</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="12" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="9"/>
@@ -1776,13 +1743,12 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-    </row>
-    <row r="30" spans="1:12">
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
         <v>29</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="9"/>
@@ -1794,13 +1760,12 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-    </row>
-    <row r="31" spans="1:12">
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
         <v>30</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="9"/>
@@ -1812,13 +1777,12 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-    </row>
-    <row r="32" spans="1:12">
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
         <v>31</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="9"/>
@@ -1830,13 +1794,12 @@
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-    </row>
-    <row r="33" spans="1:12">
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
         <v>32</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C33" s="9"/>
@@ -1848,10 +1811,9 @@
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="14"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="13"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -1862,10 +1824,9 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="14"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="13"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -1876,7 +1837,6 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
